--- a/examples/HFP_avery+quinn.xlsx
+++ b/examples/HFP_avery+quinn.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avery" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quinn" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debts" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Assets" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Avery" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Quinn" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Debts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Fixed Assets" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1557,8 +1557,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1596,6 +1600,11 @@
           <t>rate</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>property</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="b">
@@ -1622,6 +1631,11 @@
       </c>
       <c r="G2" t="n">
         <v>4</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>House</t>
+        </is>
       </c>
     </row>
   </sheetData>
